--- a/outputs/1001 TL.xlsx
+++ b/outputs/1001 TL.xlsx
@@ -10,11 +10,9 @@
     <sheet name="Agoda" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Booking.com" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Expedia" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Traveloka" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Trip.com (New)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="triplaホテルブッキング" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="じゃらん" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="楽天トラベル" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Trip.com (New)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="じゃらん" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="楽天トラベル" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -420,17 +418,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="33" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
     <col width="29" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
@@ -512,31 +510,31 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Yoshio Murai</t>
+          <t>Chung Ting Cheung</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>111031</v>
+        <v>22490</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>111031</v>
+        <v>22490</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-11 10:28:00</t>
+          <t>2026-07-25 15:15:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -545,7 +543,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -566,40 +564,40 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SEOHEE YUN</t>
+          <t>MASARU MIZUNOE</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>14053</v>
+        <v>3334</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>14053</v>
+        <v>3334</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-07-21 21:01:00</t>
+          <t>2026-07-28 19:53:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>女性専用ドミトリールーム</t>
+          <t>ドミトリー</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -620,44 +618,44 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>YUJIN KIM</t>
+          <t>ChuYue Zhang</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>30598</v>
+        <v>6340</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>30598</v>
+        <v>6340</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-07-23 13:32:00</t>
+          <t>2026-08-11 16:58:00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>女性専用ドミトリールーム</t>
+          <t>ドミトリー</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Non-refundable Rate(Dormitory Only) (SELL Inclusive)</t>
+          <t>Non-refundable Rate (with Breakfast)(Dormitory Only) (SELL Inclusive)</t>
         </is>
       </c>
     </row>
@@ -674,7 +672,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -684,21 +682,21 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>kaneta hiroyuki</t>
+          <t>Pacharaphon Yaisaeng</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>23610</v>
+        <v>10330</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>23610</v>
+        <v>10330</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-08-08 15:29:00</t>
+          <t>2026-08-14 15:30:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -707,11 +705,11 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Non-refundable Rate (with Breakfast)(Dormitory Only) (SELL Inclusive)</t>
+          <t>Non-refundable Rate(Dormitory Only) (SELL Inclusive)</t>
         </is>
       </c>
     </row>
@@ -728,40 +726,40 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Chuting Zhang</t>
+          <t>Shun Kaeriyama</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>8794</v>
+        <v>2349</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>8794</v>
+        <v>2349</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-08-09 20:46:00</t>
+          <t>2026-08-21 15:14:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>女性専用ドミトリールーム</t>
+          <t>ドミトリー</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -782,31 +780,31 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ferry Angriawan</t>
+          <t>TAKUYA NAKAGAWA</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>14865</v>
+        <v>4080</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>14865</v>
+        <v>4080</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-08-14 10:47:00</t>
+          <t>2026-09-11 12:32:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -815,11 +813,11 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Non-refundable Rate (with Breakfast)(Dormitory Only) (SELL Inclusive)</t>
+          <t>Standard Rate (SELL Inclusive)</t>
         </is>
       </c>
     </row>
@@ -836,44 +834,44 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Reina Nomura</t>
+          <t>YICHEN ZHANG</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>23148</v>
+        <v>53191</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>23148</v>
+        <v>53191</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-08-17 15:07:00</t>
+          <t>2026-09-17 18:54:00</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>スタンダード 1ダブルベッド</t>
+          <t>ドミトリー</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Non-refundable Rate（Private Room） (SELL Inclusive)</t>
+          <t>Weekly rate (SELL Inclusive)</t>
         </is>
       </c>
     </row>
@@ -890,44 +888,44 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Heamin Jang</t>
+          <t>Mei Shan Kwok</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>29348</v>
+        <v>12886</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>29348</v>
+        <v>12886</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-02 11:16:00</t>
+          <t>2026-09-26 18:28:00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>女性専用ドミトリールーム</t>
+          <t>ドミトリー</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Weekly rate (SELL Inclusive)</t>
+          <t>Standard Rate ( with Breakfast ) (SELL Inclusive)</t>
         </is>
       </c>
     </row>
@@ -944,31 +942,31 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RYUSEI IRIE</t>
+          <t>Jing Xuan Choon</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4080</v>
+        <v>10944</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4080</v>
+        <v>10944</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-09-11 19:22:00</t>
+          <t>2026-09-28 14:37:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -977,7 +975,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -998,31 +996,31 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SHINGO ISHII</t>
+          <t>seokwoo kang</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4080</v>
+        <v>52640</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>4080</v>
+        <v>52640</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-16 07:24:00</t>
+          <t>2026-09-29 23:32:00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1031,11 +1029,11 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Standard Rate (SELL Inclusive)</t>
+          <t>Weekly rate (SELL Inclusive)</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1050,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1062,21 +1060,21 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shunta Isozaki</t>
+          <t>NAMI KAKIUCHI</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9136</v>
+        <v>5036</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>9136</v>
+        <v>5036</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-09-23 17:38:00</t>
+          <t>2026-09-30 09:15:00</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1085,7 +1083,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1106,31 +1104,31 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nguyen Dao</t>
+          <t>akira fukushima</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3825</v>
+        <v>4294</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3825</v>
+        <v>4294</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-29 10:07:00</t>
+          <t>2026-09-30 11:39:00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1160,44 +1158,44 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>akira fukushima</t>
+          <t>Yijun zhang</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3825</v>
+        <v>7127</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>3825</v>
+        <v>7127</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-29 18:07:00</t>
+          <t>2026-08-11 23:31:00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ドミトリー</t>
+          <t>女性専用ドミトリールーム</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Standard Rate (SELL Inclusive)</t>
+          <t>Non-refundable Rate(Dormitory Only) (SELL Inclusive)</t>
         </is>
       </c>
     </row>
@@ -1214,44 +1212,44 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KOTONE SUGANAMI</t>
+          <t>YURIE SANO</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3825</v>
+        <v>8736</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>3825</v>
+        <v>8736</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-29 20:47:00</t>
+          <t>2026-08-26 12:40:00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>ドミトリー</t>
+          <t>スタンダード 1ダブルベッド</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Standard Rate (SELL Inclusive)</t>
+          <t>Non-refundable Rate（Private Room） (SELL Inclusive)</t>
         </is>
       </c>
     </row>
@@ -1268,40 +1266,40 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>nur hayati</t>
+          <t>Junlin Kevin Chen</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>68369</v>
+        <v>35553</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>68369</v>
+        <v>35553</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-06-07 19:32:00</t>
+          <t>2026-06-20 05:47:00</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>グループルーム B</t>
+          <t>クアッドルーム</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1310,178 +1308,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Agoda</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Czarina Agustin</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>22653</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>22653</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-08-17 04:48:00</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>女性専用ドミトリールーム</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>4</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Standard Rate ( with Breakfast ) (SELL Inclusive)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Agoda</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Kiera Cochrane</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>38496</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>38496</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-05-30 05:45:00</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ドミトリーベッド</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>9</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Non-refundable Rate (with Breakfast)(Dormitory Only) (SELL Inclusive)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Agoda</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Karolina Pernaraviciute</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>62325</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>62325</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-08-14 21:48:00</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>女性専用ドミトリールーム</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>13</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Non-refundable Rate (with Breakfast)(Dormitory Only) (SELL Inclusive)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="F20">
-        <f>SUM(F2:F19)</f>
+      <c r="F17">
+        <f>SUM(F2:F16)</f>
         <v/>
       </c>
-      <c r="G20">
-        <f>SUM(G2:G19)</f>
+      <c r="G17">
+        <f>SUM(G2:G16)</f>
         <v/>
       </c>
-      <c r="H20">
-        <f>SUM(H2:H19)</f>
+      <c r="H17">
+        <f>SUM(H2:H16)</f>
         <v/>
       </c>
     </row>
@@ -1496,14 +1332,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
@@ -1588,44 +1424,44 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Marco Eggensperger</t>
+          <t>Jules Hansen</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>191334</v>
+        <v>22206</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>191334</v>
+        <v>22206</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-04-05 00:22:34</t>
+          <t>2026-03-11 21:59:42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>和室　4人部屋</t>
+          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Standard Rate (with  Breakfast)</t>
+          <t>Standard Rate</t>
         </is>
       </c>
     </row>
@@ -1642,40 +1478,40 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Marco Eggensperger</t>
+          <t>MAEHARA ATSUSHI</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>191334</v>
+        <v>12881</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>191334</v>
+        <v>12881</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-04-05 00:22:34</t>
+          <t>2026-07-08 23:28:43</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>和室　4人部屋</t>
+          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -1696,31 +1532,31 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Juan Ignacio Vel?zquez Bernal</t>
+          <t>Tamashiro Tamami</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>46735</v>
+        <v>24736</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>46735</v>
+        <v>24736</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-08-28 09:39:58</t>
+          <t>2026-08-12 07:25:01</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1729,7 +1565,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -1750,40 +1586,40 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stacy Grimes</t>
+          <t>Thomas CAPY</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>25707</v>
+        <v>17012</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>25707</v>
+        <v>17012</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-16 21:38:04</t>
+          <t>2026-08-16 18:35:08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
+          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -1804,40 +1640,40 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Motooka Chika</t>
+          <t>Thomas CAPY</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3804</v>
+        <v>17012</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3804</v>
+        <v>17012</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-25 11:31:11</t>
+          <t>2026-08-16 18:35:08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
+          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1858,7 +1694,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1868,34 +1704,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Angelina Dadulla</t>
+          <t>Choo Jeongho</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>72097</v>
+        <v>4643</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>72097</v>
+        <v>4643</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-05-14 14:18:04</t>
+          <t>2026-08-24 11:20:09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ファミリールーム　専用バスルーム付</t>
+          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Standard Rate (with  Breakfast)</t>
+          <t>Standard Rate</t>
         </is>
       </c>
     </row>
@@ -1912,31 +1748,31 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ICHIHARA GEN</t>
+          <t>Guillermo Antonio Figueroa Rodr?guez</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>35865</v>
+        <v>13603</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>35865</v>
+        <v>13603</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-08-28 11:28:27</t>
+          <t>2026-08-29 04:17:25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1945,7 +1781,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1966,40 +1802,40 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TAMAKI KOZAKA</t>
+          <t>Yu Kozuma</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>20093</v>
+        <v>23781</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>20093</v>
+        <v>23781</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-22 18:28:11</t>
+          <t>2026-09-04 17:49:54</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
+          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -2020,40 +1856,40 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>TING LI</t>
+          <t>FUMIKO YOSHIDA</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>12722</v>
+        <v>2856</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>12722</v>
+        <v>2856</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-03 19:54:59</t>
+          <t>2026-09-06 19:45:12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
+          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -2074,7 +1910,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2084,21 +1920,21 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>hermant J?r?me</t>
+          <t>Paul Baumer</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>53823</v>
+        <v>21041</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>53823</v>
+        <v>21041</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-05 18:32:14</t>
+          <t>2026-09-10 00:14:13</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2107,7 +1943,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -2128,31 +1964,31 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kermit Leon Diaz</t>
+          <t>Tarter Maria Concepcion</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>17908</v>
+        <v>57559</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>17908</v>
+        <v>57559</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-08-30 05:56:00</t>
+          <t>2026-09-12 02:18:24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2161,7 +1997,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -2182,31 +2018,31 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Huang MinChia</t>
+          <t>Dong Xiaolong</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>12149</v>
+        <v>11828</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>12149</v>
+        <v>11828</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-24 19:38:00</t>
+          <t>2026-09-25 10:53:30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2215,7 +2051,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -2236,7 +2072,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2246,21 +2082,21 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lin Chen Kuei</t>
+          <t>Kota Ichikawa</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>26848</v>
+        <v>3902</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>26848</v>
+        <v>3902</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-09-04 05:37:02</t>
+          <t>2026-09-25 14:26:16</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2269,7 +2105,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -2290,31 +2126,31 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oktay Okan</t>
+          <t>Darius Washington</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>25839</v>
+        <v>17905</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>25839</v>
+        <v>17905</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-09-29 13:33:14</t>
+          <t>2026-09-26 05:44:34</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2323,11 +2159,11 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Standard Rate</t>
+          <t>Standard Rate (with  Breakfast)</t>
         </is>
       </c>
     </row>
@@ -2344,31 +2180,31 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HIRAMATSU KENSUKE</t>
+          <t>Anthony Grimaldi</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3685</v>
+        <v>17905</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3685</v>
+        <v>17905</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-09-29 12:46:25</t>
+          <t>2026-09-29 20:18:36</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2377,11 +2213,11 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Standard Rate</t>
+          <t>Standard Rate (with  Breakfast)</t>
         </is>
       </c>
     </row>
@@ -2398,31 +2234,31 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shubham Thakur</t>
+          <t>Miguel Nu?ez fuentes</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>72123</v>
+        <v>3316</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>72123</v>
+        <v>3316</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-09-25 20:57:01</t>
+          <t>2026-09-29 23:01:25</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2431,11 +2267,11 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Standard Rate (with  Breakfast)</t>
+          <t>Standard Rate</t>
         </is>
       </c>
     </row>
@@ -2452,44 +2288,44 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>TOKUNAGA ERIKA</t>
+          <t>Narayan Ashok Bhat</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>10271</v>
+        <v>13143</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>10271</v>
+        <v>13143</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-09-21 18:18:14</t>
+          <t>2026-09-29 23:31:57</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
+          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Standard Rate</t>
+          <t>Standard Rate (with  Breakfast)</t>
         </is>
       </c>
     </row>
@@ -2506,36 +2342,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ozaki Junko</t>
+          <t>MAKOTO YAMANAKA</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>20995</v>
+        <v>3960</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>20995</v>
+        <v>3960</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-09-19 15:40:21</t>
+          <t>2026-09-29 23:58:49</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>ファミリールーム　専用バスルーム付</t>
+          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2543,7 +2379,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Standard Rate</t>
+          <t>Standard Rate (with  Breakfast)</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2396,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2570,21 +2406,21 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Brendan Lindicy</t>
+          <t>Dica Puspita</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>160243</v>
+        <v>3942</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>160243</v>
+        <v>3942</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-04-05 16:26:56</t>
+          <t>2026-09-30 06:11:40</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2593,11 +2429,11 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Standard Rate (with  Breakfast)</t>
+          <t>Standard Rate</t>
         </is>
       </c>
     </row>
@@ -2614,40 +2450,40 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Omar Tarik Khalaf</t>
+          <t>Dica Puspita</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>28353</v>
+        <v>3942</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>28353</v>
+        <v>3942</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-04-26 05:29:17</t>
+          <t>2026-09-30 06:11:40</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>トリプルルーム　共用バスルーム</t>
+          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2668,40 +2504,40 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dallas Marita Pahiri</t>
+          <t>Berkay Torunoglu</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>9700</v>
+        <v>23366</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>9700</v>
+        <v>23366</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-09-24 11:46:43</t>
+          <t>2026-09-30 10:34:48</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
+          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -2722,7 +2558,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2732,21 +2568,21 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sehee Yoon</t>
+          <t>田中 元生</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2506</v>
+        <v>3893</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2506</v>
+        <v>3893</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-08-26 12:03:00</t>
+          <t>2026-09-30 13:42:40</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2755,7 +2591,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2776,31 +2612,31 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LU YUXING</t>
+          <t>Woods Noah</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>39793</v>
+        <v>64813</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>39793</v>
+        <v>64813</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-08-22 19:13:01</t>
+          <t>2026-08-13 16:07:16</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2809,7 +2645,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2830,44 +2666,44 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Zeina Ziud diaz vasquez</t>
+          <t>Miss Aylint? Hooper</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>13951</v>
+        <v>24542</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>13951</v>
+        <v>24542</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:12</t>
+          <t>2026-09-29 19:21:46</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
+          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Standard Rate (with  Breakfast)</t>
+          <t>Standard Rate</t>
         </is>
       </c>
     </row>
@@ -2884,31 +2720,31 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ilsur Gabdulkhakov</t>
+          <t>Haekal Adzani</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3316</v>
+        <v>70230</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>3316</v>
+        <v>70230</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-26 11:31:38</t>
+          <t>2026-09-30 01:39:05</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2917,7 +2753,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -2938,40 +2774,40 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Surendra Kumar Yadav</t>
+          <t>Shuk Ki Chan</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>25730</v>
+        <v>29020</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>25730</v>
+        <v>29020</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-05-29 14:10:15</t>
+          <t>2026-05-15 00:58:15</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>トリプルルーム　共用バスルーム</t>
+          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -2992,40 +2828,40 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fabian Hellriegel</t>
+          <t>amada chihiro</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>11220</v>
+        <v>2547</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>11220</v>
+        <v>2547</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-28 11:17:22</t>
+          <t>2026-09-02 00:27:47</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
+          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -3046,40 +2882,40 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lars Reschke</t>
+          <t>Janee McNeil</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>21998</v>
+        <v>47428</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>21998</v>
+        <v>47428</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-05-10 05:46:52</t>
+          <t>2026-09-14 03:43:15</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">クイーンルーム　</t>
+          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3100,40 +2936,40 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>?亮 ?</t>
+          <t>Nika Jakesch</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>29404</v>
+        <v>11928</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>29404</v>
+        <v>11928</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-20 22:42:05</t>
+          <t>2026-09-29 03:25:30</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
+          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -3154,31 +2990,31 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sophie Gerdina Reith</t>
+          <t>yuko yoshikuni</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>25809</v>
+        <v>5480</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>25809</v>
+        <v>5480</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-07-13 19:11:59</t>
+          <t>2026-09-30 16:49:15</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3187,11 +3023,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Standard Rate (with  Breakfast)</t>
+          <t>Standard Rate</t>
         </is>
       </c>
     </row>
@@ -3208,40 +3044,40 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Roi Shoen Guttman</t>
+          <t>MENGSHU LIU</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>11275</v>
+        <v>52205</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>11275</v>
+        <v>52205</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-26 17:18:49</t>
+          <t>2026-09-26 22:13:53</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
+          <t>ドミトリールーム（6人部屋）　男女共用</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -3262,36 +3098,36 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Koizumi Nobukazu</t>
+          <t>MENGSHU LIU</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4643</v>
+        <v>55618</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>4643</v>
+        <v>55618</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-08-17 22:56:02</t>
+          <t>2026-09-26 22:13:53</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
+          <t>ドミトリールーム（6人部屋）　男女共用</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -3299,7 +3135,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Standard Rate</t>
+          <t>Run of the House rate</t>
         </is>
       </c>
     </row>
@@ -3316,44 +3152,44 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CHUANG CHIEHWEI</t>
+          <t>MENGSHU LIU</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>98686</v>
+        <v>32425</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>98686</v>
+        <v>32425</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-06-06 20:18:04</t>
+          <t>2026-09-26 22:20:07</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>ファミリールーム　専用バスルーム付</t>
+          <t>ドミトリールーム　男女共用</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Standard Rate</t>
+          <t>Run of the House rate</t>
         </is>
       </c>
     </row>
@@ -3370,7 +3206,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3380,34 +3216,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>He? Vailea</t>
+          <t>MENGSHU LIU</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>18115</v>
+        <v>53446</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>18115</v>
+        <v>53446</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-08-16 18:43:38</t>
+          <t>2026-09-26 22:20:07</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
+          <t>スタンダード　トリプルルーム</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Standard Rate (with  Breakfast)</t>
+          <t>Standard Rate</t>
         </is>
       </c>
     </row>
@@ -3424,40 +3260,40 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chung Hooi Yip</t>
+          <t>MENGSHU LIU</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>12130</v>
+        <v>53446</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>12130</v>
+        <v>53446</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-08-16 15:04:16</t>
+          <t>2026-09-26 22:20:07</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
+          <t>スタンダード　トリプルルーム</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -3478,7 +3314,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3488,30 +3324,30 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shingu Mitsuki</t>
+          <t>MENGSHU LIU</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>24423</v>
+        <v>66519</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>24423</v>
+        <v>66519</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-09-22 00:20:28</t>
+          <t>2026-09-26 22:13:53</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
+          <t>ファミリールーム　専用バスルーム付</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -3532,40 +3368,40 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Haekal Adzani</t>
+          <t>MENGSHU LIU</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>34841</v>
+        <v>66519</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>34841</v>
+        <v>66519</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-09-21 23:20:45</t>
+          <t>2026-09-26 22:13:53</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
+          <t>ファミリールーム　専用バスルーム付</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -3586,31 +3422,31 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jessica Dawes</t>
+          <t>慶之 髙島</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>79939</v>
+        <v>21482</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>79939</v>
+        <v>21482</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-07-19 19:15:02</t>
+          <t>2026-09-29 19:33:07</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3619,11 +3455,11 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Standard Rate</t>
+          <t>Standard Rate (with  Breakfast)</t>
         </is>
       </c>
     </row>
@@ -3640,44 +3476,44 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Miura Ayu</t>
+          <t>Katrine Freds?e</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>6215</v>
+        <v>11729</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>6215</v>
+        <v>11729</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-07-21 20:59:32</t>
+          <t>2026-09-28 03:10:30</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
+          <t>トリプルルーム　共用バスルーム</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Standard Rate</t>
+          <t>Standard Rate (with  Breakfast)</t>
         </is>
       </c>
     </row>
@@ -3694,1030 +3530,58 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Beyza Ayg?n</t>
+          <t>マキコ 田野</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>19067</v>
+        <v>103407</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>19067</v>
+        <v>103407</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-07-28 04:45:04</t>
+          <t>2026-07-20 19:58:57</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
+          <t>ファミリールーム　専用バスルーム付</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Standard Rate</t>
+          <t>Standard Rate (with  Breakfast)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Nishiyama Mizuho</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>5591</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>5591</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-07-24 18:40:53</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>2</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Standard Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Kuron Vega</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>73064</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>73064</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-09-23 10:08:39</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
-        </is>
-      </c>
-      <c r="K43" t="n">
-        <v>14</v>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Standard Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Praparnrat Chitrungsakorn</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>31109</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>31109</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-09-02 13:21:29</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
-        <v>9</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Standard Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Emerson Quituizaca</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>22110</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>22110</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-09-02 17:50:03</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
-        </is>
-      </c>
-      <c r="K45" t="n">
-        <v>8</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Standard Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Ajay Sohal</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>13003</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>13003</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2026-08-29 18:24:43</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
-        </is>
-      </c>
-      <c r="K46" t="n">
-        <v>4</v>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Standard Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Holger Schlaps</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>20775</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>20775</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2026-09-11 16:31:31</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
-        <v>4</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Standard Rate (with  Breakfast)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Mateus De Nardo Moura</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>49027</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>49027</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2026-09-11 00:42:07</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
-        </is>
-      </c>
-      <c r="K48" t="n">
-        <v>12</v>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Standard Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Hasegawa Akane</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>119427</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>119427</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2026-08-13 00:21:20</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
-        </is>
-      </c>
-      <c r="K49" t="n">
-        <v>30</v>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Standard Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Sven Gebauer</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>27076</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>27076</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-09-22 14:04:35</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
-        </is>
-      </c>
-      <c r="K50" t="n">
-        <v>8</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Standard Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Alana Okeeffe</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>58476</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>58476</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2026-08-07 05:21:23</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>ドミトリールーム　女性用　二段ベッド1名分</t>
-        </is>
-      </c>
-      <c r="K51" t="n">
-        <v>12</v>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Standard Rate (with  Breakfast)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Nathalia Lestary</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>89777</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>89777</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2026-06-11 20:02:23</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>4人部屋　シャワー付</t>
-        </is>
-      </c>
-      <c r="K52" t="n">
-        <v>6</v>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Standard Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>XIE GUANG ZHE</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>55598</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>55598</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2026-07-20 12:23:29</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>ダブルルーム</t>
-        </is>
-      </c>
-      <c r="K53" t="n">
-        <v>5</v>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Standard Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>HIDEKAZU KODERA</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>22819</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>22819</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2026-08-26 14:10:28</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
-        </is>
-      </c>
-      <c r="K54" t="n">
-        <v>11</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Standard Rate (with  Breakfast)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2026-09-26</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Thomas Ford</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>21990</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>21990</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2026-08-29 21:54:33</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>7</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Standard Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Miss Aylint? Hooper</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>26671</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>26671</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2026-09-17 18:34:24</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
-        </is>
-      </c>
-      <c r="K56" t="n">
-        <v>7</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Standard Rate (with  Breakfast)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Surya Kant Mani</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>59846</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>59846</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2026-07-23 11:28:37</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
-        </is>
-      </c>
-      <c r="K57" t="n">
-        <v>14</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Standard Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>sergi calor</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>27975</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>27975</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2026-09-14 06:56:43</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>ドミトリールーム　男女共用　二段ベッド1名分</t>
-        </is>
-      </c>
-      <c r="K58" t="n">
-        <v>8</v>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Standard Rate</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Booking.com</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>廖 芯平</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>65170</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>65170</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2026-05-06 23:11:53</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>スタンダード　トリプルルーム</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
-        <v>4</v>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Standard Rate (with  Breakfast)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="F60">
-        <f>SUM(F2:F59)</f>
+      <c r="F42">
+        <f>SUM(F2:F41)</f>
         <v/>
       </c>
-      <c r="G60">
-        <f>SUM(G2:G59)</f>
+      <c r="G42">
+        <f>SUM(G2:G41)</f>
         <v/>
       </c>
-      <c r="H60">
-        <f>SUM(H2:H59)</f>
+      <c r="H42">
+        <f>SUM(H2:H41)</f>
         <v/>
       </c>
     </row>
@@ -4732,21 +3596,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="29" customWidth="1" min="9" max="9"/>
-    <col width="92" customWidth="1" min="10" max="10"/>
+    <col width="80" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="62" customWidth="1" min="12" max="12"/>
+    <col width="47" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4824,40 +3688,40 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MUHAMAD RIZKY SOPIAN</t>
+          <t>akira taguchi</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>23897</v>
+        <v>6847</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>18867</v>
+        <v>5407</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-05-24 20:37:00</t>
+          <t>2026-09-10 00:46:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Shared Dormitory, Mixed Dorm, Non Smoking</t>
+          <t xml:space="preserve">Mixed Dormitory Room (Shared Shower &amp; Toilet) </t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -4878,44 +3742,44 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hsinyin Chang</t>
+          <t>RIVO YUDHINATA BRIAN NUGRAHA</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>31720</v>
+        <v>29914</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>25044</v>
+        <v>23620</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-02 20:32:00</t>
+          <t>2026-09-16 23:09:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Private Group Room for 4-6 with Shared Shower room, Non Smoking</t>
+          <t xml:space="preserve">Mixed Dormitory Room (Shared Shower &amp; Toilet) </t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Room Only non-refundable(N NR_NB)</t>
+          <t>Standard Rate non-refundable(N SR_NB)</t>
         </is>
       </c>
     </row>
@@ -4932,31 +3796,31 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SUNGKYUNG KWAK</t>
+          <t>RIN YAMADA</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>34364</v>
+        <v>6834</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>27133</v>
+        <v>5395</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-08-25 06:23:00</t>
+          <t>2026-09-08 14:22:00</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -4965,7 +3829,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -4986,7 +3850,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4996,21 +3860,21 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Justine Junek</t>
+          <t>Iku Ichimori</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>13857</v>
+        <v>3950</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>10938</v>
+        <v>3119</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-09-08 19:56:00</t>
+          <t>2026-09-11 22:31:00</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -5019,11 +3883,11 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Standard Rate(with Breakfast) non-refundable(N SR_B)</t>
+          <t>Standard Rate(N SR_NB)</t>
         </is>
       </c>
     </row>
@@ -5040,7 +3904,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5050,34 +3914,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>hendrik orissanto</t>
+          <t>Hinata Sakamoto</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>94668</v>
+        <v>12792</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>74742</v>
+        <v>10100</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-09-08 23:24:00</t>
+          <t>2026-09-23 01:20:00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Private Family Room for 6-8 with Private Shower room, Non Smoking</t>
+          <t>Female Single Dormitory Bed, Non Smoking (Bunk Bed)</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Room Only non-refundable(PKG-NNR_NB)</t>
+          <t>Standard Rate(N SR_NB)</t>
         </is>
       </c>
     </row>
@@ -5094,7 +3958,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -5104,210 +3968,48 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Michel Raymond</t>
+          <t>SUNGHYUN LIM</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>14049</v>
+        <v>63606</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>11093</v>
+        <v>52264</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-09-11 15:45:00</t>
+          <t>2026-07-29 09:55:00</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mixed Dormitory Room (Shared Shower &amp; Toilet) </t>
+          <t>Private Room for 4 with Private Shower room, Non Smoking (2 Bunk Beds)</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Standard Rate non-refundable(N SR_NB)</t>
+          <t>Room Only non-refundable(N NR_NB)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Expedia</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>カード決済</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>NAOKI KOMIYAMA</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>16175</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>12772</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-09-12 12:28:00</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mixed Dormitory Room (Shared Shower &amp; Toilet) </t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>4</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Standard Rate non-refundable(N SR_NB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Expedia</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>カード決済</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Kevin A Esquivel</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>33482</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>26438</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-09-15 11:42:00</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Mixed Single Dormitory Bed, Non Smoking (Bunk Bed)</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>3Days Rate（Room Only）(N 3DR_NB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Expedia</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>カード決済</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Basarat Ghasemi</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>8505</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>6714</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-09-29 03:43:00</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Private Group Room for 1-3 with Shared Shower room, Non Smoking (Queen Bed + Sofa)</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Room Only(PKG-NSR_NB)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="F11">
-        <f>SUM(F2:F10)</f>
+      <c r="F8">
+        <f>SUM(F2:F7)</f>
         <v/>
       </c>
-      <c r="G11">
-        <f>SUM(G2:G10)</f>
+      <c r="G8">
+        <f>SUM(G2:G7)</f>
         <v/>
       </c>
-      <c r="H11">
-        <f>SUM(H2:H10)</f>
+      <c r="H8">
+        <f>SUM(H2:H7)</f>
         <v/>
       </c>
     </row>
@@ -5325,18 +4027,18 @@
   <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="37" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="29" customWidth="1" min="9" max="9"/>
-    <col width="32" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="32" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5404,7 +4106,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Traveloka</t>
+          <t>Trip.com (New)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5414,51 +4116,51 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nicolas Rama Prasetya</t>
+          <t>POULIQUEN ELISE</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>46935</v>
+        <v>18365</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>46935</v>
+        <v>18365</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-08-08 13:42:54</t>
+          <t>2026-09-04 04:30:55</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>男女共用ドミトリールーム（1BED）</t>
+          <t>Bed in Mixed Dormitory Room (Bunk Bed) (Mixed Gender)</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>キャンセル不可プラン（素泊り）</t>
+          <t>キャンセル不可プラン（素泊り）※ドミトリー</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Traveloka</t>
+          <t>Trip.com (New)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5468,51 +4170,51 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>icefaresontop icefaresontop</t>
+          <t>Takeda Erina</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>27384</v>
+        <v>15134</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>27384</v>
+        <v>15134</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-23 19:54:20</t>
+          <t>2026-09-30 10:29:59</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>男女共用シングルドミトリールーム（1BED）</t>
+          <t>Bed in Mixed Single Dormitory Room (Bunk Bed) (Mixed Gender)</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>キャンセル不可プラン（素泊り）</t>
+          <t>3Days Rate（素泊まり）※ドミトリー</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Traveloka</t>
+          <t>Trip.com (New)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5522,7 +4224,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5532,34 +4234,34 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TOHRU YOKOI</t>
+          <t>CAO SIMIN</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>32072</v>
+        <v>4095</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>32072</v>
+        <v>4095</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-09-03 00:59:44</t>
+          <t>2026-09-15 14:21:42</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>男女共用ドミトリールーム（1BED）</t>
+          <t>Bed in Female Dormitory Room (Bunk Bed) (Female Only)</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>スタンダードプラン（朝食付き）</t>
+          <t>スタンダードプラン（素泊り）</t>
         </is>
       </c>
     </row>
@@ -5588,1349 +4290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="29" customWidth="1" min="9" max="9"/>
-    <col width="70" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="32" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>予約サイト名</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>支払方法</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>チェックイン日</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>チェックアウト日</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>宿泊者氏名</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>合計料金</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ポイント</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>請求料金</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>予約日時</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>部屋名称</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>泊数</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>プラン名称</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>QIN YUYAO</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>10547</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>10547</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-08-09 02:17:07</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Bed In Mixed Dormitory Bed (Bunk Bed) (Mixed Gender)</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>キャンセル不可プラン（素泊り）※ドミトリー</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>YU SHIHAN</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>6514</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6514</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-08-12 23:22:53</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Bed In Female Single Dormitory Bed (Bunk Bed) (Female Only)</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>キャンセル不可プラン（素泊り）※ドミトリー</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>HOU QINGNAN</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>3931</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3931</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-08-21 02:41:59</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Bed In Mixed Dormitory Bed (Bunk Bed) (Mixed Gender)</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>キャンセル不可プラン（素泊り）※ドミトリー</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>LAI CONGHUI</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>14732</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>14732</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-08-29 03:29:23</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Bed in Mixed Dormitory Room (Bunk Bed) (Mixed Gender)</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>5</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>キャンセル不可プラン（素泊り）※ドミトリー</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>YANG NALI</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>2995</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>2995</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-08-31 22:24:01</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Bed in Female Dormitory Room (Bunk Bed) (Female Only)</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>キャンセル不可プラン（素泊り）※ドミトリー</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>WANG XI</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>5990</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5990</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-08-31 22:30:29</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Bed in Female Dormitory Room (Bunk Bed) (Female Only)</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>キャンセル不可プラン（素泊り）※ドミトリー</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Turikov Ivan</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>25868</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>25868</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-09-03 12:52:48</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Bed in Mixed Dormitory Room (Bunk Bed) (Mixed Gender)</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>キャンセル不可プラン（朝食付）※ドミトリー</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>XIE TIANYU</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>2711</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2711</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-09-04 14:35:16</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Bed in Mixed Dormitory Room (Bunk Bed) (Mixed Gender)</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>キャンセル不可プラン（朝食付）※ドミトリー</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>YUAN MENG</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>9086</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>9086</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-09-04 17:13:59</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Bed in Mixed Dormitory Room (Bunk Bed) (Mixed Gender)</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>キャンセル不可プラン（素泊り）※ドミトリー</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ELMUDIR GIAAKI WISAM</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>27187</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>27187</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-09-11 20:31:06</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Bed in Mixed Dormitory Room (Bunk Bed) (Mixed Gender)</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>7</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>3Days Rate（素泊まり）※ドミトリー</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>SHIU WING HONG</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>59044</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>59044</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-07-06 21:54:02</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Bed In Mixed Dormitory Bed (Bunk Bed) (Mixed Gender)</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>キャンセル不可プラン（素泊り）※ドミトリー</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LAU CHI HANG</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>26399</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>26399</v>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-08-24 23:22:27</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Bed In Mixed Dormitory Bed (Bunk Bed) (Mixed Gender)</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>8</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>キャンセル不可プラン（朝食付）※ドミトリー</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>HIDAYATI NUR RACMA</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>8834</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>8834</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-08-12 12:41:40</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Bed In Female Dormitory Bed (Bunk Bed) (Female Only)</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>キャンセル不可プラン（素泊り）※ドミトリー</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>OTA TSUYOSHI</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>5737</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>5737</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-08-25 12:59:25</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Bed In Mixed Dormitory Bed (Bunk Bed) (Mixed Gender)</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>キャンセル不可プラン（素泊り）※ドミトリー</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>seito mami</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>27823</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>27823</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-09-23 14:40:05</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Bed in Mixed Single Dormitory Room (Bunk Bed) (Mixed Gender)</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>3Days Rate（素泊まり）※ドミトリー</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>WAKAMOTO YOSHITAKA</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>12136</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>12136</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-09-27 15:38:40</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Bed in Mixed Dormitory Room (Bunk Bed) (Mixed Gender)</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>4</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>3Days Rate（素泊まり）※ドミトリー</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>KIM JUNYEON</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>3570</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>3570</v>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-09-26 00:20:23</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Bed in Mixed Dormitory Room (Bunk Bed) (Mixed Gender)</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>1</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>スタンダードプラン（素泊り）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>KIM SUNCHEOL</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>33140</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>33140</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-09-26 14:23:55</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Bed in Mixed Dormitory Room (Bunk Bed) (Mixed Gender)</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>7</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>3Days Rate（素泊まり）※ドミトリー</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Trip.com (New)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>ALSHEHRI BADER ALI A</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>39750</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>39750</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-08-25 06:17:15</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Private Room For 4 With Private Bathroom (2 Bunk Beds)</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>4</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>キャンセル不可プラン（素泊り）※個室</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="F21">
-        <f>SUM(F2:F20)</f>
-        <v/>
-      </c>
-      <c r="G21">
-        <f>SUM(G2:G20)</f>
-        <v/>
-      </c>
-      <c r="H21">
-        <f>SUM(H2:H20)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:L4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="29" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="33" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>予約サイト名</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>支払方法</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>チェックイン日</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>チェックアウト日</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>宿泊者氏名</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>合計料金</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ポイント</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>請求料金</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>予約日時</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>部屋名称</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>泊数</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>プラン名称</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>triplaホテルブッキング</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ほくえ さあや</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>5920</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>5920</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-08-28 16:22:43</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ドミトリールーム　男女共用　</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>2</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>スタンダードプラン※キャンセル不可（朝食付き）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>triplaホテルブッキング</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>事前決済</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>やの かずこ</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>16758</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>16758</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-09-28 08:12:52</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ドミトリールーム　女性専用</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>スタンダードプラン （素泊まり）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="F4">
-        <f>SUM(F2:F3)</f>
-        <v/>
-      </c>
-      <c r="G4">
-        <f>SUM(G2:G3)</f>
-        <v/>
-      </c>
-      <c r="H4">
-        <f>SUM(H2:H3)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6942,9 +4302,9 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="29" customWidth="1" min="9" max="9"/>
-    <col width="37" customWidth="1" min="10" max="10"/>
+    <col width="33" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="38" customWidth="1" min="12" max="12"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7022,44 +4382,44 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>園田 寛子</t>
+          <t>川口 正和</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12480</v>
+        <v>2800</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>2500</v>
       </c>
       <c r="H2" t="n">
-        <v>11480</v>
+        <v>300</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-08-22 06:34:00</t>
+          <t>2026-08-30 19:27:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>シングルドミトリー　女性専用　（二段ベッド×1）</t>
+          <t>ドミトリールーム　男女共用　（二段ベッド×1）</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>【じゃらんのお得な10日間】スタンダードプラン※素泊まり</t>
+          <t>【じゃらんスペシャルウィーク】限定シンプルプラン（素泊まり）</t>
         </is>
       </c>
     </row>
@@ -7076,31 +4436,31 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>瀬川 美涼</t>
+          <t>鹿嶋 美優</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4880</v>
+        <v>11408</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="H3" t="n">
-        <v>4780</v>
+        <v>10308</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-09-19 08:48:00</t>
+          <t>2026-09-14 20:21:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -7109,133 +4469,25 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>シンプルプラン（素泊まり）</t>
+          <t>【じゃらんスペシャルウィーク】限定シンプルプラン（素泊まり）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>じゃらん</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>カード決済</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>松尾 和樹</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>50520</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>49520</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-09-28 18:46:00</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>ドミトリールーム　男女共用　（二段ベッド×1）</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>シンプルプラン（素泊まり）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>じゃらん</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>カード決済</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>佐藤 真人</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>13200</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>12200</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-09-28 18:49:00</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>3名グループ個室（共用シャワールーム&amp;amp;トイレ）</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>シンプルプラン（素泊まり）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="F6">
-        <f>SUM(F2:F5)</f>
+      <c r="F4">
+        <f>SUM(F2:F3)</f>
         <v/>
       </c>
-      <c r="G6">
-        <f>SUM(G2:G5)</f>
+      <c r="G4">
+        <f>SUM(G2:G3)</f>
         <v/>
       </c>
-      <c r="H6">
-        <f>SUM(H2:H5)</f>
+      <c r="H4">
+        <f>SUM(H2:H3)</f>
         <v/>
       </c>
     </row>
@@ -7244,7 +4496,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7257,14 +4509,14 @@
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
     <col width="29" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="29" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7342,44 +4594,44 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>川口 小百合</t>
+          <t>デスタ プラタマ</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5430</v>
+        <v>32160</v>
       </c>
       <c r="G2" t="n">
-        <v>597</v>
+        <v>4823</v>
       </c>
       <c r="H2" t="n">
-        <v>4833</v>
+        <v>27337</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-09-23 04:28:58</t>
+          <t>2026-09-29 14:57:22</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>シングルドミトリー　女性専用</t>
+          <t>【個室】クイーンベッド×1（1～3名）※共用シャワー・トイレ</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>素泊まりシンプルプラン</t>
+          <t>【楽天スーパーSALE】素泊まりプラン</t>
         </is>
       </c>
     </row>
